--- a/plate3d/PLATE3D_HINGE.xlsx
+++ b/plate3d/PLATE3D_HINGE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="61">
   <si>
     <t>DEVICE (HINGE) - step 1: the back plate and the camera wall plate</t>
   </si>
@@ -85,7 +85,7 @@
     <t>ho.bay</t>
   </si>
   <si>
-    <t>ho.step</t>
+    <t>ho.shld</t>
   </si>
   <si>
     <t>two bays beside the tab, the 30 step in the top, and 4-D22</t>
@@ -155,9 +155,6 @@
   </si>
   <si>
     <t>XZ</t>
-  </si>
-  <si>
-    <t>YZ</t>
   </si>
   <si>
     <t>BASE</t>
@@ -769,7 +766,7 @@
         <v>14</v>
       </c>
       <c r="F8">
-        <v>645</v>
+        <v>205</v>
       </c>
       <c r="G8">
         <v>40</v>
@@ -842,7 +839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -861,6 +858,15 @@
       <c r="F12" t="s">
         <v>24</v>
       </c>
+      <c r="G12">
+        <v>645</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -984,16 +990,16 @@
         <v>14</v>
       </c>
       <c r="F17">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>-7.5</v>
       </c>
       <c r="H17">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1007,13 +1013,13 @@
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
         <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1027,7 +1033,7 @@
         <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
         <v>11</v>
@@ -1038,28 +1044,28 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="C22" t="s">
         <v>2</v>
       </c>
       <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" t="s">
         <v>53</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>54</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>55</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>56</v>
-      </c>
-      <c r="H22" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1067,16 +1073,16 @@
         <v>17</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
         <v>58</v>
-      </c>
-      <c r="C23" t="s">
-        <v>59</v>
       </c>
       <c r="D23" t="s">
         <v>46</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F23">
         <v>-415</v>
@@ -1093,7 +1099,7 @@
         <v>17</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
